--- a/files/availability-list-august-2026.xlsx
+++ b/files/availability-list-august-2026.xlsx
@@ -2006,7 +2006,7 @@
         <v>28.5</v>
       </c>
       <c r="G75" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76">
@@ -2300,7 +2300,7 @@
         <v>60</v>
       </c>
       <c r="G89" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90">
@@ -3329,7 +3329,7 @@
         <v>25.5</v>
       </c>
       <c r="G138" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="139">
@@ -5618,7 +5618,7 @@
         <v>24</v>
       </c>
       <c r="G247" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="248">
@@ -5933,7 +5933,7 @@
         <v>25.5</v>
       </c>
       <c r="G262" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="263">
@@ -6500,7 +6500,7 @@
         <v>65</v>
       </c>
       <c r="G289" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="290">
@@ -10259,7 +10259,7 @@
         <v>24</v>
       </c>
       <c r="G468" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="469">

--- a/files/availability-list-august-2026.xlsx
+++ b/files/availability-list-august-2026.xlsx
@@ -3432,11 +3432,7 @@
           <t>100 - 125</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>.0</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
         <v>25.5</v>
       </c>
@@ -3542,11 +3538,7 @@
           <t>150 - 200</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>.0</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
         <v>31.5</v>
       </c>
@@ -3716,11 +3708,7 @@
           <t>100 - 125</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>.0</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
         <v>25.5</v>
       </c>
@@ -4326,11 +4314,7 @@
           <t>50 - 75</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>.0</t>
-        </is>
-      </c>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
         <v>25.5</v>
       </c>
@@ -6148,11 +6132,7 @@
           <t>60 - 90</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>.0</t>
-        </is>
-      </c>
+      <c r="F165" t="inlineStr"/>
       <c r="G165" t="n">
         <v>18</v>
       </c>
@@ -8200,11 +8180,7 @@
           <t>150 - 200</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>.0</t>
-        </is>
-      </c>
+      <c r="F225" t="inlineStr"/>
       <c r="G225" t="n">
         <v>37.5</v>
       </c>
@@ -8238,11 +8214,7 @@
           <t>150 - 200</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>.0</t>
-        </is>
-      </c>
+      <c r="F226" t="inlineStr"/>
       <c r="G226" t="n">
         <v>37.5</v>
       </c>
@@ -8718,11 +8690,7 @@
           <t>140 - 160</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>.0</t>
-        </is>
-      </c>
+      <c r="F240" t="inlineStr"/>
       <c r="G240" t="n">
         <v>37.5</v>
       </c>
@@ -10412,11 +10380,7 @@
           <t>150 - 200</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>.0</t>
-        </is>
-      </c>
+      <c r="F289" t="inlineStr"/>
       <c r="G289" t="n">
         <v>37.5</v>
       </c>
@@ -10772,11 +10736,7 @@
           <t>100 - 125</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>.0</t>
-        </is>
-      </c>
+      <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
         <v>28.5</v>
       </c>
@@ -11740,11 +11700,7 @@
           <t>90 - 120</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>.0</t>
-        </is>
-      </c>
+      <c r="F327" t="inlineStr"/>
       <c r="G327" t="n">
         <v>25.5</v>
       </c>
@@ -11910,11 +11866,7 @@
         </is>
       </c>
       <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>.0</t>
-        </is>
-      </c>
+      <c r="F332" t="inlineStr"/>
       <c r="G332" t="n">
         <v>12</v>
       </c>
@@ -12734,11 +12686,7 @@
           <t>100 - 125</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>.0</t>
-        </is>
-      </c>
+      <c r="F356" t="inlineStr"/>
       <c r="G356" t="n">
         <v>28.5</v>
       </c>
@@ -13732,11 +13680,7 @@
           <t>100 - 125</t>
         </is>
       </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>.0</t>
-        </is>
-      </c>
+      <c r="F385" t="inlineStr"/>
       <c r="G385" t="n">
         <v>31.5</v>
       </c>
